--- a/shiny/gene_explorer/genes_of_interest.xlsx
+++ b/shiny/gene_explorer/genes_of_interest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mgierlinski/Work/Projects/BetaReg/BetaReg_ST/shiny/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mgierlinski/Work/Projects/BetaReg/BetaReg_ST/shiny/gene_explorer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B33C82-00D7-8F4F-9295-863AA889BCC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F957C8-8FFE-EE4A-8DD1-71BED7763FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39200" yWindow="1500" windowWidth="21640" windowHeight="20100" firstSheet="6" activeTab="9" xr2:uid="{07E91300-B98E-49DE-A2FA-A40FAA3F0CBD}"/>
+    <workbookView xWindow="29560" yWindow="1500" windowWidth="21640" windowHeight="20100" firstSheet="7" activeTab="13" xr2:uid="{07E91300-B98E-49DE-A2FA-A40FAA3F0CBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Insulin Signalling" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,8 @@
     <sheet name="Schwann cell" sheetId="6" r:id="rId10"/>
     <sheet name="Metabolic commitment " sheetId="11" r:id="rId11"/>
     <sheet name="Cell Cylce Regulation" sheetId="13" r:id="rId12"/>
+    <sheet name="T1D risk genes" sheetId="16" r:id="rId13"/>
+    <sheet name="T2D risk genes" sheetId="17" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="789">
   <si>
     <t>INSR</t>
   </si>
@@ -2754,6 +2756,60 @@
   </si>
   <si>
     <t>NGFR</t>
+  </si>
+  <si>
+    <t>PPY</t>
+  </si>
+  <si>
+    <t>RSBN1</t>
+  </si>
+  <si>
+    <t>ATXN2</t>
+  </si>
+  <si>
+    <t>IL2RA</t>
+  </si>
+  <si>
+    <t>CTLA4</t>
+  </si>
+  <si>
+    <t>CLEC16A</t>
+  </si>
+  <si>
+    <t>TCF7L2</t>
+  </si>
+  <si>
+    <t>BACH2</t>
+  </si>
+  <si>
+    <t>UBASH3A</t>
+  </si>
+  <si>
+    <t>FAP</t>
+  </si>
+  <si>
+    <t>RNLS</t>
+  </si>
+  <si>
+    <t>APOBR</t>
+  </si>
+  <si>
+    <t>CDKN2B</t>
+  </si>
+  <si>
+    <t>CDKAL1</t>
+  </si>
+  <si>
+    <t>CDKN1C</t>
+  </si>
+  <si>
+    <t>IGF2BP2</t>
+  </si>
+  <si>
+    <t>FTO</t>
+  </si>
+  <si>
+    <t>HHEX</t>
   </si>
 </sst>
 </file>
@@ -5183,9 +5239,144 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1295B8-F7D0-704C-8513-78816CD7DCCF}">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>782</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{748D60B5-0182-C540-B73B-F058C1DE8E43}">
+  <dimension ref="A1:A11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>592</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ADC1A72-EB4A-DF4A-A8E8-19CA77394530}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -5276,6 +5467,11 @@
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>553</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>771</v>
       </c>
     </row>
   </sheetData>
